--- a/docs/Työajan seuranta Valtteri.xlsx
+++ b/docs/Työajan seuranta Valtteri.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhaj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{090EBF8A-BB39-43C9-9B04-B72367ECF3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C116DA29-0867-4300-AFFD-E91AF124BB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -53,34 +53,71 @@
     <t>low fidelity wireframe</t>
   </si>
   <si>
+    <t xml:space="preserve">2h </t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Ui search (home navbar)</t>
+  </si>
+  <si>
+    <t>8h</t>
+  </si>
+  <si>
+    <t>43h 10min</t>
+  </si>
+  <si>
+    <t>Ui Search (home navbar search)</t>
+  </si>
+  <si>
+    <t>6h</t>
+  </si>
+  <si>
+    <t>Ui search page ja now in theaters page loppuun</t>
+  </si>
+  <si>
+    <t>6h 30 min</t>
+  </si>
+  <si>
+    <t>Implement Login API and Auth</t>
+  </si>
+  <si>
     <t>2h</t>
   </si>
   <si>
-    <t>Ui search (home navbar)</t>
-  </si>
-  <si>
-    <t>8h</t>
-  </si>
-  <si>
-    <t>Ui Search (home navbar search)</t>
-  </si>
-  <si>
-    <t>6h</t>
-  </si>
-  <si>
-    <t>Ui search page ja now in theaters page loppuun</t>
-  </si>
-  <si>
-    <t>6.5h</t>
-  </si>
-  <si>
-    <t>Implement Login API and Auth</t>
-  </si>
-  <si>
     <t xml:space="preserve">shared login url </t>
   </si>
   <si>
     <t>5h</t>
+  </si>
+  <si>
+    <t>implement add movies to group</t>
+  </si>
+  <si>
+    <t>4h</t>
+  </si>
+  <si>
+    <t>group delete by owner
+fixes changes &amp; added tests</t>
+  </si>
+  <si>
+    <t>5h 30 min</t>
+  </si>
+  <si>
+    <t>presentation planning ideas</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>presentation  plan changes</t>
+  </si>
+  <si>
+    <t>planning req table &amp;powerpoint</t>
+  </si>
+  <si>
+    <t>2h 10min</t>
   </si>
 </sst>
 </file>
@@ -104,7 +141,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -112,19 +149,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,24 +506,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BC3D70-9A8B-4A59-8343-1D3356DFB267}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -466,8 +534,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:6">
+      <c r="A3" s="3">
         <v>46271</v>
       </c>
       <c r="B3" t="s">
@@ -476,60 +544,121 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
+      <c r="F3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3">
         <v>46276</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
+        <v>8</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3">
         <v>46277</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3">
         <v>46278</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3">
         <v>46281</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3">
         <v>46292</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3">
+        <v>46296</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1">
+      <c r="A10" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3">
+        <v>46307</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3">
+        <v>46308</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3">
+        <v>46309</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -538,23 +667,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BAF6AFB37B6774A9122C6036818BC92" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c611cd0fe7e35dfe638a44e659100205">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44038759-07ae-40d4-bc3d-7c9fb0b3775b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="36a43d4c38ea7f7b42b5de64d2c1c906" ns3:_="">
     <xsd:import namespace="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
@@ -734,16 +846,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
